--- a/ig/main/ValueSet-jdv-j333-activite-sanitaire-diverse-regulee-niv1-finess.xlsx
+++ b/ig/main/ValueSet-jdv-j333-activite-sanitaire-diverse-regulee-niv1-finess.xlsx
@@ -7,13 +7,14 @@
   </bookViews>
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
-    <sheet name="Include #0" r:id="rId4" sheetId="2"/>
+    <sheet name="Expansion Parameters" r:id="rId4" sheetId="2"/>
+    <sheet name="Expansion" r:id="rId5" sheetId="3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="51">
   <si>
     <t>Property</t>
   </si>
@@ -66,15 +67,12 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-05T18:02:28.249+00:00</t>
+    <t>2026-05-29T09:12:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>Agence du Numérique en Santé (ANS) - 2-10 Rue d'Oradour-sur-Glane, 75015 Paris</t>
-  </si>
-  <si>
     <t>Jurisdiction</t>
   </si>
   <si>
@@ -84,9 +82,6 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Jeu de valeurs FINESS contenant toutes les Activités Sanitaires Diverses Régulées (ASDR) de niveau 1</t>
-  </si>
-  <si>
     <t>Purpose</t>
   </si>
   <si>
@@ -99,25 +94,79 @@
     <t>BooleanType[null]</t>
   </si>
   <si>
-    <t>Operation</t>
-  </si>
-  <si>
-    <t>niveau</t>
-  </si>
-  <si>
-    <t>=</t>
+    <t>Parameter</t>
+  </si>
+  <si>
+    <t>used-codesystem</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/tre-r347-activite-sanitaire-diverse-regulee|20260505120000</t>
+  </si>
+  <si>
+    <t>version</t>
+  </si>
+  <si>
+    <t>Level</t>
+  </si>
+  <si>
+    <t>System</t>
+  </si>
+  <si>
+    <t>Code</t>
+  </si>
+  <si>
+    <t>Display</t>
+  </si>
+  <si>
+    <t>Abstract</t>
+  </si>
+  <si>
+    <t>Inactive</t>
   </si>
   <si>
     <t>1</t>
   </si>
   <si>
+    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/tre-r347-activite-sanitaire-diverse-regulee</t>
+  </si>
+  <si>
+    <t>0500</t>
+  </si>
+  <si>
+    <t>Accueil et Réception des Urgences</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
-    <t>System URI</t>
-  </si>
-  <si>
-    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/tre-r347-activite-sanitaire-diverse-regulee</t>
+    <t>0600</t>
+  </si>
+  <si>
+    <t>Autres Disciplines Sanitaires</t>
+  </si>
+  <si>
+    <t>0400</t>
+  </si>
+  <si>
+    <t>Disciplines Médico-Techniques</t>
+  </si>
+  <si>
+    <t>0300</t>
+  </si>
+  <si>
+    <t>Disciplines Spécifiques</t>
+  </si>
+  <si>
+    <t>0200</t>
+  </si>
+  <si>
+    <t>Hospitalisation</t>
+  </si>
+  <si>
+    <t>0800</t>
+  </si>
+  <si>
+    <t>Lutte contre les Toxicomanies</t>
   </si>
 </sst>
 </file>
@@ -334,44 +383,40 @@
       <c r="A10" t="s" s="2">
         <v>18</v>
       </c>
-      <c r="B10" t="s" s="2">
-        <v>19</v>
-      </c>
+      <c r="B10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="B11" t="s" s="2">
         <v>20</v>
-      </c>
-      <c r="B11" t="s" s="2">
-        <v>21</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="B12" t="s" s="2">
-        <v>23</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="B12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -381,49 +426,190 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
-  <cols>
-    <col min="1" max="1" width="30.703125" customWidth="true"/>
-    <col min="2" max="2" width="50.703125" customWidth="true"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>28</v>
-      </c>
-      <c r="C1" t="s" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>30</v>
-      </c>
-      <c r="C2" t="s" s="2">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
+        <v>29</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:G7"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>30</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>31</v>
+      </c>
+      <c r="C1" t="s" s="1">
+        <v>29</v>
+      </c>
+      <c r="D1" t="s" s="1">
         <v>32</v>
       </c>
+      <c r="E1" t="s" s="1">
+        <v>33</v>
+      </c>
+      <c r="F1" t="s" s="1">
+        <v>34</v>
+      </c>
+      <c r="G1" t="s" s="1">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="E2" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="F2" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G2" t="s" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>36</v>
+      </c>
       <c r="B3" t="s" s="2">
-        <v>32</v>
+        <v>37</v>
+      </c>
+      <c r="C3" s="2"/>
+      <c r="D3" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="E3" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="F3" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G3" t="s" s="2">
+        <v>15</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>34</v>
+        <v>37</v>
+      </c>
+      <c r="C4" s="2"/>
+      <c r="D4" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="E4" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="F4" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G4" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C5" s="2"/>
+      <c r="D5" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="E5" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="F5" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G5" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B6" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C6" s="2"/>
+      <c r="D6" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="E6" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="F6" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G6" t="s" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B7" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C7" s="2"/>
+      <c r="D7" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="E7" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="F7" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G7" t="s" s="2">
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/ig/main/ValueSet-jdv-j333-activite-sanitaire-diverse-regulee-niv1-finess.xlsx
+++ b/ig/main/ValueSet-jdv-j333-activite-sanitaire-diverse-regulee-niv1-finess.xlsx
@@ -7,14 +7,13 @@
   </bookViews>
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
-    <sheet name="Expansion Parameters" r:id="rId4" sheetId="2"/>
-    <sheet name="Expansion" r:id="rId5" sheetId="3"/>
+    <sheet name="Include #0" r:id="rId4" sheetId="2"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="35">
   <si>
     <t>Property</t>
   </si>
@@ -67,12 +66,15 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-29T09:12:29+00:00</t>
+    <t>2026-05-05T18:02:28.249+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
+    <t>Agence du Numérique en Santé (ANS) - 2-10 Rue d'Oradour-sur-Glane, 75015 Paris</t>
+  </si>
+  <si>
     <t>Jurisdiction</t>
   </si>
   <si>
@@ -82,6 +84,9 @@
     <t>Description</t>
   </si>
   <si>
+    <t>Jeu de valeurs FINESS contenant toutes les Activités Sanitaires Diverses Régulées (ASDR) de niveau 1</t>
+  </si>
+  <si>
     <t>Purpose</t>
   </si>
   <si>
@@ -94,79 +99,25 @@
     <t>BooleanType[null]</t>
   </si>
   <si>
-    <t>Parameter</t>
-  </si>
-  <si>
-    <t>used-codesystem</t>
-  </si>
-  <si>
-    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/tre-r347-activite-sanitaire-diverse-regulee|20260505120000</t>
-  </si>
-  <si>
-    <t>version</t>
-  </si>
-  <si>
-    <t>Level</t>
-  </si>
-  <si>
-    <t>System</t>
-  </si>
-  <si>
-    <t>Code</t>
-  </si>
-  <si>
-    <t>Display</t>
-  </si>
-  <si>
-    <t>Abstract</t>
-  </si>
-  <si>
-    <t>Inactive</t>
+    <t>Operation</t>
+  </si>
+  <si>
+    <t>niveau</t>
+  </si>
+  <si>
+    <t>=</t>
   </si>
   <si>
     <t>1</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
+    <t>System URI</t>
+  </si>
+  <si>
     <t>https://smt.esante.gouv.fr/fhir/CodeSystem/tre-r347-activite-sanitaire-diverse-regulee</t>
-  </si>
-  <si>
-    <t>0500</t>
-  </si>
-  <si>
-    <t>Accueil et Réception des Urgences</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>0600</t>
-  </si>
-  <si>
-    <t>Autres Disciplines Sanitaires</t>
-  </si>
-  <si>
-    <t>0400</t>
-  </si>
-  <si>
-    <t>Disciplines Médico-Techniques</t>
-  </si>
-  <si>
-    <t>0300</t>
-  </si>
-  <si>
-    <t>Disciplines Spécifiques</t>
-  </si>
-  <si>
-    <t>0200</t>
-  </si>
-  <si>
-    <t>Hospitalisation</t>
-  </si>
-  <si>
-    <t>0800</t>
-  </si>
-  <si>
-    <t>Lutte contre les Toxicomanies</t>
   </si>
 </sst>
 </file>
@@ -383,40 +334,44 @@
       <c r="A10" t="s" s="2">
         <v>18</v>
       </c>
-      <c r="B10" s="2"/>
+      <c r="B10" t="s" s="2">
+        <v>19</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="B12" s="2"/>
+        <v>22</v>
+      </c>
+      <c r="B12" t="s" s="2">
+        <v>23</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -426,190 +381,49 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="30.703125" customWidth="true"/>
+    <col min="2" max="2" width="50.703125" customWidth="true"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="B1" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="C1" t="s" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>28</v>
+        <v>30</v>
+      </c>
+      <c r="C2" t="s" s="2">
+        <v>31</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>28</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:G7"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s" s="1">
-        <v>30</v>
-      </c>
-      <c r="B1" t="s" s="1">
-        <v>31</v>
-      </c>
-      <c r="C1" t="s" s="1">
-        <v>29</v>
-      </c>
-      <c r="D1" t="s" s="1">
         <v>32</v>
-      </c>
-      <c r="E1" t="s" s="1">
-        <v>33</v>
-      </c>
-      <c r="F1" t="s" s="1">
-        <v>34</v>
-      </c>
-      <c r="G1" t="s" s="1">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="B2" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="C2" s="2"/>
-      <c r="D2" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="E2" t="s" s="2">
-        <v>39</v>
-      </c>
-      <c r="F2" t="s" s="2">
-        <v>15</v>
-      </c>
-      <c r="G2" t="s" s="2">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="C3" s="2"/>
-      <c r="D3" t="s" s="2">
-        <v>41</v>
-      </c>
-      <c r="E3" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="F3" t="s" s="2">
-        <v>15</v>
-      </c>
-      <c r="G3" t="s" s="2">
-        <v>15</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="C4" s="2"/>
-      <c r="D4" t="s" s="2">
-        <v>43</v>
-      </c>
-      <c r="E4" t="s" s="2">
-        <v>44</v>
-      </c>
-      <c r="F4" t="s" s="2">
-        <v>15</v>
-      </c>
-      <c r="G4" t="s" s="2">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="B5" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="C5" s="2"/>
-      <c r="D5" t="s" s="2">
-        <v>45</v>
-      </c>
-      <c r="E5" t="s" s="2">
-        <v>46</v>
-      </c>
-      <c r="F5" t="s" s="2">
-        <v>15</v>
-      </c>
-      <c r="G5" t="s" s="2">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="B6" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="C6" s="2"/>
-      <c r="D6" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="E6" t="s" s="2">
-        <v>48</v>
-      </c>
-      <c r="F6" t="s" s="2">
-        <v>15</v>
-      </c>
-      <c r="G6" t="s" s="2">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="B7" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="C7" s="2"/>
-      <c r="D7" t="s" s="2">
-        <v>49</v>
-      </c>
-      <c r="E7" t="s" s="2">
-        <v>50</v>
-      </c>
-      <c r="F7" t="s" s="2">
-        <v>15</v>
-      </c>
-      <c r="G7" t="s" s="2">
-        <v>15</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>

--- a/ig/main/ValueSet-jdv-j333-activite-sanitaire-diverse-regulee-niv1-finess.xlsx
+++ b/ig/main/ValueSet-jdv-j333-activite-sanitaire-diverse-regulee-niv1-finess.xlsx
@@ -8,12 +8,14 @@
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Include #0" r:id="rId4" sheetId="2"/>
+    <sheet name="Expansion Parameters" r:id="rId5" sheetId="3"/>
+    <sheet name="Expansion" r:id="rId6" sheetId="4"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="57">
   <si>
     <t>Property</t>
   </si>
@@ -118,6 +120,72 @@
   </si>
   <si>
     <t>https://smt.esante.gouv.fr/fhir/CodeSystem/tre-r347-activite-sanitaire-diverse-regulee</t>
+  </si>
+  <si>
+    <t>Parameter</t>
+  </si>
+  <si>
+    <t>used-codesystem</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/tre-r347-activite-sanitaire-diverse-regulee|20260601120000</t>
+  </si>
+  <si>
+    <t>version</t>
+  </si>
+  <si>
+    <t>Level</t>
+  </si>
+  <si>
+    <t>System</t>
+  </si>
+  <si>
+    <t>Code</t>
+  </si>
+  <si>
+    <t>Display</t>
+  </si>
+  <si>
+    <t>Abstract</t>
+  </si>
+  <si>
+    <t>Inactive</t>
+  </si>
+  <si>
+    <t>0500</t>
+  </si>
+  <si>
+    <t>Accueil et Réception des Urgences</t>
+  </si>
+  <si>
+    <t>0600</t>
+  </si>
+  <si>
+    <t>Autres Disciplines Sanitaires</t>
+  </si>
+  <si>
+    <t>0400</t>
+  </si>
+  <si>
+    <t>Disciplines Médico-Techniques</t>
+  </si>
+  <si>
+    <t>0300</t>
+  </si>
+  <si>
+    <t>Disciplines Spécifiques</t>
+  </si>
+  <si>
+    <t>0200</t>
+  </si>
+  <si>
+    <t>Hospitalisation</t>
+  </si>
+  <si>
+    <t>0800</t>
+  </si>
+  <si>
+    <t>Lutte contre les Toxicomanies</t>
   </si>
 </sst>
 </file>
@@ -429,4 +497,197 @@
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>37</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:G7"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>39</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>40</v>
+      </c>
+      <c r="C1" t="s" s="1">
+        <v>38</v>
+      </c>
+      <c r="D1" t="s" s="1">
+        <v>41</v>
+      </c>
+      <c r="E1" t="s" s="1">
+        <v>42</v>
+      </c>
+      <c r="F1" t="s" s="1">
+        <v>43</v>
+      </c>
+      <c r="G1" t="s" s="1">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="E2" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="F2" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G2" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C3" s="2"/>
+      <c r="D3" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="E3" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="F3" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G3" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C4" s="2"/>
+      <c r="D4" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="E4" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="F4" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G4" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C5" s="2"/>
+      <c r="D5" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="E5" t="s" s="2">
+        <v>52</v>
+      </c>
+      <c r="F5" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G5" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="B6" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C6" s="2"/>
+      <c r="D6" t="s" s="2">
+        <v>53</v>
+      </c>
+      <c r="E6" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="F6" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G6" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="B7" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C7" s="2"/>
+      <c r="D7" t="s" s="2">
+        <v>55</v>
+      </c>
+      <c r="E7" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="F7" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G7" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
 </file>
--- a/ig/main/ValueSet-jdv-j333-activite-sanitaire-diverse-regulee-niv1-finess.xlsx
+++ b/ig/main/ValueSet-jdv-j333-activite-sanitaire-diverse-regulee-niv1-finess.xlsx
@@ -128,7 +128,7 @@
     <t>used-codesystem</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/tre-r347-activite-sanitaire-diverse-regulee|20260601120000</t>
+    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/tre-r347-activite-sanitaire-diverse-regulee|20260629120000</t>
   </si>
   <si>
     <t>version</t>

--- a/ig/main/ValueSet-jdv-j333-activite-sanitaire-diverse-regulee-niv1-finess.xlsx
+++ b/ig/main/ValueSet-jdv-j333-activite-sanitaire-diverse-regulee-niv1-finess.xlsx
@@ -8,14 +8,12 @@
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Include #0" r:id="rId4" sheetId="2"/>
-    <sheet name="Expansion Parameters" r:id="rId5" sheetId="3"/>
-    <sheet name="Expansion" r:id="rId6" sheetId="4"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="35">
   <si>
     <t>Property</t>
   </si>
@@ -120,72 +118,6 @@
   </si>
   <si>
     <t>https://smt.esante.gouv.fr/fhir/CodeSystem/tre-r347-activite-sanitaire-diverse-regulee</t>
-  </si>
-  <si>
-    <t>Parameter</t>
-  </si>
-  <si>
-    <t>used-codesystem</t>
-  </si>
-  <si>
-    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/tre-r347-activite-sanitaire-diverse-regulee|20260629120000</t>
-  </si>
-  <si>
-    <t>version</t>
-  </si>
-  <si>
-    <t>Level</t>
-  </si>
-  <si>
-    <t>System</t>
-  </si>
-  <si>
-    <t>Code</t>
-  </si>
-  <si>
-    <t>Display</t>
-  </si>
-  <si>
-    <t>Abstract</t>
-  </si>
-  <si>
-    <t>Inactive</t>
-  </si>
-  <si>
-    <t>0500</t>
-  </si>
-  <si>
-    <t>Accueil et Réception des Urgences</t>
-  </si>
-  <si>
-    <t>0600</t>
-  </si>
-  <si>
-    <t>Autres Disciplines Sanitaires</t>
-  </si>
-  <si>
-    <t>0400</t>
-  </si>
-  <si>
-    <t>Disciplines Médico-Techniques</t>
-  </si>
-  <si>
-    <t>0300</t>
-  </si>
-  <si>
-    <t>Disciplines Spécifiques</t>
-  </si>
-  <si>
-    <t>0200</t>
-  </si>
-  <si>
-    <t>Hospitalisation</t>
-  </si>
-  <si>
-    <t>0800</t>
-  </si>
-  <si>
-    <t>Lutte contre les Toxicomanies</t>
   </si>
 </sst>
 </file>
@@ -497,197 +429,4 @@
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s" s="1">
-        <v>35</v>
-      </c>
-      <c r="B1" t="s" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="B2" t="s" s="2">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>37</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:G7"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s" s="1">
-        <v>39</v>
-      </c>
-      <c r="B1" t="s" s="1">
-        <v>40</v>
-      </c>
-      <c r="C1" t="s" s="1">
-        <v>38</v>
-      </c>
-      <c r="D1" t="s" s="1">
-        <v>41</v>
-      </c>
-      <c r="E1" t="s" s="1">
-        <v>42</v>
-      </c>
-      <c r="F1" t="s" s="1">
-        <v>43</v>
-      </c>
-      <c r="G1" t="s" s="1">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="B2" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="C2" s="2"/>
-      <c r="D2" t="s" s="2">
-        <v>45</v>
-      </c>
-      <c r="E2" t="s" s="2">
-        <v>46</v>
-      </c>
-      <c r="F2" t="s" s="2">
-        <v>15</v>
-      </c>
-      <c r="G2" t="s" s="2">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="C3" s="2"/>
-      <c r="D3" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="E3" t="s" s="2">
-        <v>48</v>
-      </c>
-      <c r="F3" t="s" s="2">
-        <v>15</v>
-      </c>
-      <c r="G3" t="s" s="2">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="C4" s="2"/>
-      <c r="D4" t="s" s="2">
-        <v>49</v>
-      </c>
-      <c r="E4" t="s" s="2">
-        <v>50</v>
-      </c>
-      <c r="F4" t="s" s="2">
-        <v>15</v>
-      </c>
-      <c r="G4" t="s" s="2">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="B5" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="C5" s="2"/>
-      <c r="D5" t="s" s="2">
-        <v>51</v>
-      </c>
-      <c r="E5" t="s" s="2">
-        <v>52</v>
-      </c>
-      <c r="F5" t="s" s="2">
-        <v>15</v>
-      </c>
-      <c r="G5" t="s" s="2">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="B6" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="C6" s="2"/>
-      <c r="D6" t="s" s="2">
-        <v>53</v>
-      </c>
-      <c r="E6" t="s" s="2">
-        <v>54</v>
-      </c>
-      <c r="F6" t="s" s="2">
-        <v>15</v>
-      </c>
-      <c r="G6" t="s" s="2">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="B7" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="C7" s="2"/>
-      <c r="D7" t="s" s="2">
-        <v>55</v>
-      </c>
-      <c r="E7" t="s" s="2">
-        <v>56</v>
-      </c>
-      <c r="F7" t="s" s="2">
-        <v>15</v>
-      </c>
-      <c r="G7" t="s" s="2">
-        <v>15</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
 </file>